--- a/public/data/db-source/freq.xlsx
+++ b/public/data/db-source/freq.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bassim/code/datannur/datannur_dev/public/data/db-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F559D0EA-9954-7D4B-A8BF-057F396ECDD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AA3C883-3018-8F45-B3E3-D5B98AE58145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="29">
   <si>
     <t>value</t>
   </si>
@@ -89,6 +89,24 @@
   </si>
   <si>
     <t>montagne</t>
+  </si>
+  <si>
+    <t>emploi_jeunes__nationalite</t>
+  </si>
+  <si>
+    <t>aaaaaa</t>
+  </si>
+  <si>
+    <t>aaaaaaaaa</t>
+  </si>
+  <si>
+    <t>aaa-aaaaaa</t>
+  </si>
+  <si>
+    <t>aaa-aaaaaa-999999999-9999999999-999999999</t>
+  </si>
+  <si>
+    <t>aaaaaaaaa9999999999999999999aaaaaaaaaaa9999999999aaaaa9999</t>
   </si>
 </sst>
 </file>
@@ -169,8 +187,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6673E3E-F092-B843-96DC-BE1B5C5F51B8}" name="Tableau3" displayName="Tableau3" ref="A1:C20" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A1:C20" xr:uid="{B6673E3E-F092-B843-96DC-BE1B5C5F51B8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6673E3E-F092-B843-96DC-BE1B5C5F51B8}" name="Tableau3" displayName="Tableau3" ref="A1:C25" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:C25" xr:uid="{B6673E3E-F092-B843-96DC-BE1B5C5F51B8}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{F479AE5F-1828-5E4C-A23B-6285A48F29B3}" name="variable_id" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{84C4D4A2-8ACD-B045-91A5-EBA02C626C87}" name="value" dataDxfId="1"/>
@@ -467,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -696,6 +714,61 @@
         <v>9481</v>
       </c>
     </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="1">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
